--- a/logs/response_log.xlsx
+++ b/logs/response_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,44 +417,617 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>User Query</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bot Response</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Time Taken (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Session ID</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval Confidence (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Faithfulness</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Answer Relevance</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-Validation (SQL vs. RAG)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Link Validity</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:02:43</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>What is the attendance criteria?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+Hey there, future TKRCETian! I'm stoked to be your friendly College Buddy. Don't worry about those typos or unclear questions - we'll get everything sorted out.
+So, you want to know about attendance? Well, let me break it down for you:
+**Attendance Criteria:**
+* Attendance is calculated per subject.
+* The minimum requirement is **75% attendance**, as per JNTUH norms. This means if you miss a class, you need to make up for it by attending the next one.
+Here's a simple way to think about it:
+* If you attend all your classes for a particular subject, that's 100%.
+* If you miss one class but attend the next two, that's 80% (2/3).
+* And so on...
+**Why is attendance important?**
+* It helps you keep up with the coursework and assignments.
+* It shows your commitment to learning and participating in classes.
+* Good attendance can also improve your overall performance in exams.
+Now, I know what you're thinking: "What if I miss a class due to personal reasons?" Don't worry, we've got that covered too! If you need to take a leave, just head to the **College Office** and submit a leave application. They'll help you sort it out.
+Hope this helps, mate! Do you have any more questions about attendance or anything else?
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>90.3380</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>a2c078d8-96ec-46fe-b791-aefa7d1ee045</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:02:48</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What is the NAAC grade of the college?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A+ Grade
+📌 **Quick Links:**
+• [NAAC](https://tkrcet.ac.in/naac-2/)
+</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.0215</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>bfa19142-509f-474c-afd4-eafb69a78e7d</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:03:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tell me placement statistics.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Placements](https://tkrcet.ac.in/placements/)
+Hey there! I'm your friendly TKRCET College Buddy. I'm super excited to help you with all your queries about our amazing college!
+Firstly, let's talk about the placement stats. We're really proud of what we've achieved here at TKRCET. Here are some key numbers:
+* **Total Placed Students:** 351 (as of my last update)
+* **Placement Rate:** 21% (which is pretty impressive if I do say so myself!)
+* **Top Recruiters:**
+ + Savantis: 56 students
+ + Ncr Atleos: 38 students
+ + Dexterity: 35 students
+These numbers are a testament to our Training &amp; Placement Cell's hard work in connecting us with top companies. Our cell focuses on providing continuous student training, company tie-ups, and mock interviews to ensure we're all ready for the real world.
+If you want to know more about our placement process or would like to check out our current job openings, I recommend visiting our college website or contacting our Training &amp; Placement Cell directly. They'll be able to give you the most up-to-date info!
+How's that? Do you have any other questions about TKRCET or placements?
+📚 **Source Links:**
+• [Placements](https://tkrcet.ac.in/placements/)
+</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56.4692</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>117a5cdb-f8cb-431b-9d6e-e9e2b4b9e49a</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:05:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>where the college is located?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Hey there, future TKRCETian! I'm stoked to be your friendly College Buddy. Don't worry if you have any questions or need help with anything - I've got your back!
+So, you're looking for some info about our amazing college, right? Well, let me tell you, we're proud of what we do here at TKRCET.
+First off, regarding your questions:
+* We don't have a medical facility on campus, but we do have a tie-up with nearby hospitals and medical centers. If you need any serious medical attention, our staff will help you get in touch with the right people.
+* Our college was indeed established in **2002**, and it's been growing ever since!
+* The contact number of the college is indeed **+91 9849477550**. You can give them a call if you need any info or just want to chat.
+Now, about your question: Where is our college located? Well, we're situated in Hyderabad, Telangana, India! Specifically, our address is:
+**TKRCET College**
+**Near Kukatpally Cross Road**
+**Hyderabad, Telangana - 500072**
+We're easily accessible by public transport or even a short drive from the city center. If you need help finding us, just ask anyone around, and they'll point you in the right direction!
+By the way, did you know that we have a pretty cool campus life here at TKRCET? We've got awesome facilities, including sports fields, libraries, and more! Our students are always busy with extracurricular activities, clubs, and whatnot.
+If you have any more questions or just want to chat about TKRCET, feel free to ask me anytime! I'm all ears (and ready to help).
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>67.6896</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7fb761db-301a-462b-84de-b3f198e51718</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:05:11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>What courses are offered in the College?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Courses Offered:**
+🎓 **B.Tech:** CSE, CSE-AIML, CSE-DS, ECE, EEE, IT, Mechanical, Civil
+🎓 **M.Tech/MBA:** M.Tech in CSE, M.Tech in Power Electronics, MBA
+📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0006</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ec4cf31c-cf18-40fc-81af-f51593a8ffa3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:06:54</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>How to check the results?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Hey there! I'm super excited to help you with all your TKRCET-related queries. Don't worry about any typos or unclear questions - we'll get everything sorted out!
+So, you want to know how to check the results? Easy peasy! Here's what you need to do:
+**Step 1: Visit the College Website**
+Head over to our college website ([insert website URL]) and navigate to the "Results" section. You can usually find it under the "Student Corner" or "Academic" tab.
+**Step 2: Click on the Relevant Exam**
+Look for the exam you want to check results for (e.g., B.Tech I Year I Sem, MBA II Yr I &amp; II Sem, etc.). Click on that link to proceed.
+**Step 3: Enter Your Roll Number and Other Details**
+You'll need to enter your roll number, student ID, or other required details to access the result page. Make sure you have these details handy!
+**Step 4: Download/Print Your Results**
+Once you've entered all the necessary details, click on the "Download" or "Print" button to get your results. You can usually download a PDF copy of your results.
+That's it! If you're still having trouble finding the results section or need help with anything else, feel free to ask, and I'll guide you through it.
+By the way, have you checked out our college's social media pages? We often post updates about exam schedules, result announcements, and other important notifications. You can find us on Facebook ([insert Facebook URL]) and Twitter ([insert Twitter URL]).
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100.8505</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>174601ae-6b3d-47fb-afcd-9c30d36cc89f</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:07:57</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>what is the minimum attendance required?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm stoked to help you out with all your TKRCET-related queries! So, let's get started!
+You're right that we don't have the exact info on the title and source for attendance calculation. But I can definitely guide you on how it works.
+According to JNTUH norms, **75% attendance** is mandatory per subject. This means if you miss a class or two, but attend most of your classes, you'll still be considered as having attended 75%. However, if you miss more than 25% of the total classes in a semester, you might not be able to pass that particular subject.
+Now, about the minimum attendance requirement... Since it's mandatory to have **75% attendance** per subject, I'd say the minimum overall attendance requirement is also around 75%. However, please note that this can vary depending on the specific rules and regulations of each department or faculty within the college.
+To get more accurate info, I recommend checking with your department's office or the student affairs office. They should be able to provide you with the most up-to-date information on attendance requirements.
+Also, just a heads-up: if you're having trouble meeting the attendance requirement, there are some options available to help you catch up. For example, some departments offer special classes or make-ups for students who miss classes due to illness or other reasons.
+Let me know if you have any more questions or concerns! I'm here to help
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>59.8691</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0a492e42-0464-43f6-ad85-1867265c3390</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:08:59</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do college have any dress code or uniform</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+You're looking for info about the dress code at TKRCET! Don't worry, I've got you covered!
+According to our college guidelines, yes, there is a dress code policy in place. Students are expected to follow the dress code guidelines, which generally recommend formal attire.
+Here's a quick rundown of what you can expect:
+• **Dress Code:** Formal and neat attire is recommended.
+• **Uniform:** No specific uniform is required, but students are encouraged to wear college-approved casual wear.
+• **No Jeans or Torn Clothes:** Sorry, jeans and torn clothes aren't allowed on campus!
+• **Respectful Attire:** Avoid revealing or provocative clothing that may be considered disrespectful.
+If you're unsure about what's acceptable, you can always check with the college administration or your department head (like Dr. A. Suresh Rao, our HoD of CSE and Dean Academics) for guidance.
+By the way, have you checked out our college's website or social media channels? They usually post updates on important policies and guidelines!
+Let me know if you have any other questions!
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>59.6646</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>cdc4b3ad-8b7f-424e-8112-021be9f15287</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/logs/response_log.xlsx
+++ b/logs/response_log.xlsx
@@ -1,40 +1,381 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19200" windowHeight="6800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +383,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1034,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1043,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G169"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
+  <cols>
+    <col width="27.5454545454545" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -450,6 +1083,7372 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>Accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:20:05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>What are the details for College Timings?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>**College Timings:**
+🕐 9:40 AM to 4:20 PM (Monday-Saturday)
+**Lunch Break:** 12:40 PM to 1:20 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.0168</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:20:16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What is the contact for HOD of Civil?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>For **Civil**, the HOD is **Mr. K.V.R Satya Sai**.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.0033</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:20:27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Where is the ECE Department?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.0065</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:22:24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>How do I get to the Administrative Block?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Related Resource](https://ieeexplore.ieee.org/Xplore/guesthome.jsp?reload=true)
+• [TKRCET Official Page](https://tkrcet.ac.in/student-welfare/)
+To get to the Administrative Block, you can follow these steps:
+1. Check your college map or ask a fellow student for directions.
+2. The Administrative Block is usually located at the center of the campus.
+3. If you're still unsure, try asking someone from the Student Welfare Committee (as
+📚 **Source Links:**
+• https://ieeexplore.ieee.org/Xplore/guesthome.jsp?reload=true
+• https://tkrcet.ac.in/student-welfare/
+</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>107.4826</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:22:32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Is the Administrative Block open?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Related Resource](https://ieeexplore.ieee.org/Xplore/guesthome.jsp?reload=true)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+I'd be happy to help you with your question!
+Unfortunately, I couldn't find any information about the current opening hours or status of the Administrative Block at TKR College Of Engineering &amp; Technology. However, I can suggest some options to help you get an answer:
+1. **Check the college website
+📚 **Source Links:**
+• https://ieeexplore.ieee.org/Xplore/guesthome.jsp?reload=true
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>55.7501</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:24:07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Does the college have a Gym?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+Unfortunately, I don't have direct access to the information provided in the website. However, based on the content of the website, it appears that TKR College Of Engineering &amp; Technology does not provide a dedicated "Page not found" section for their facilities or services.
+However, after searching through the website
+📚 **Source Links:**
+• https://tkrcet.ac.in/placement-news/student-placement-details
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>54.6054</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:24:17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>What is the contact for Principal?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The Principal of TKRCET is **Dr. D. V. Ravi Shankar**.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.0107</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:25:40</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I want to know about Research.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Related Resource](https://nlist.inflibnet.ac.in/veresources.php)
+• [TKRCET Official Page](https://tkrcet.ac.in/sexual-harassments/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/virtual-labs/)
+Research is an exciting and crucial part of the academic journey. At INFLIBNET Centre, Gandhinagar, we have a program called N-LIST (National Library and Information Services Network) that provides various research facilities and resources for students and researchers.
+Here are some key things you might want to
+📚 **Source Links:**
+• https://nlist.inflibnet.ac.in/veresources.php
+• https://tkrcet.ac.in/sexual-harassments/
+• https://tkrcet.ac.in/facilities/virtual-labs/
+</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>52.9835</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:26:32</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Where can I find the Main Gate?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/gallary-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+The Main Gate of TKR College Of Engineering &amp; Technology is located on the college campus. If you're having trouble finding it, I recommend checking out a campus map or asking any of the staff members for directions. They'll be able to point you in the right direction.
+Alternatively, if you have
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/gallary-2/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>48.7308</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:27:29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tell me about Examinations.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Exam timings vary by semester and course. Please refer to the exam timetable published by the college on the notice board or website.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.5513</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:28:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Is there a Wi-Fi on campus?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+Yes, I can help you with that.
+According to the TKR College of Engineering and Technology website, they have a state-of-the-art campus infrastructure, including:
+* Open-air auditorium
+* Mini-auditorium
+* Modern classrooms
+* Library
+* Wi-Fi connectivity is available on
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>57.1712</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:31:50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How much is the fee for 1st year?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0099</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:32:56</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Where can I find the Basketball Court?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+I'd be happy to help you find the Basketball Court at TKR College Of Engineering &amp; Technology!
+According to the facilities section on their website, the Sports section has information about various facilities available for students. You can check out their website and look for the "Sports" page.
+Specifically, they
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/facilities/sports/
+</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>50.6386</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:32:58</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>How can I contact the HOD of IT?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>**Dr. R. Muruanantham** heads the **IT** department.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0402</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:33:15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>I want to know about Medical Facilities.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>State-of-the-art labs, smart classrooms, Wi-Fi campus, digital library, hostel (boys &amp; girls), transport, sports ground, auditorium, NCC, incubation center, and medical facilities.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.9395</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:34:06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tell me about Dress Code.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/code-of-conduct/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+Hello!
+At TKRCET, we have a dress code policy in place to ensure that students maintain a professional and respectful atmosphere on campus. Here are the guidelines:
+**Dress Code Policy:**
+* The dress code is formal and modest.
+* Students are required to wear school-provided uniforms or
+📚 **Source Links:**
+• https://tkrcet.ac.in/code-of-conduct/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>44.2365</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:34:52</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>How do I get to the Gymnasium?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+Unfortunately, there isn't any information about a gymnasium on the webpage you provided.
+However, based on the layout of the webpage, it appears that the Sports section is not directly linked to any physical facilities such as a gymnasium. The webpage only mentions outdoor sports like cricket and football,
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>44.4578</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:34:54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>How much is the fee for 1st year?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.0016</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:35:41</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tell me about Industrial Visits.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+Industrial Visits!
+At our institution, we believe that hands-on experience and exposure to real-world industries are essential for students' growth and development. As part of our curriculum, we organize regular industrial visits to various companies and organizations in and around Hyderabad.
+These visits provide students with an opportunity to witness firsthand
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/transport/
+• https://tkrcet.ac.in/events-2/
+</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>44.6984</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:36:28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Is the Hostel open?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+Unfortunately, I don't see any information about the hostel being open or closed. The provided text only seems to be related to transportation fees and schedules for a school or college. If you're looking for information about the hostel, I'd suggest checking with the college administration or searching online for the specific hostel
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/facilities/transport/
+</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>42.8606</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:37:17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>I want to know about Canteen Menu.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>**College Canteen**
+The college canteen provides hygienic food, snacks, and beverages at subsidized rates. It is a clean and spacious area where students can relax and refuel.
+**Menu:** South Indian, North Indian, Chinese snacks, and beverages.
+**Timings:** Open during college hours (including lunch break).</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.1212</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:37:27</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>What is the fee structure for 4th year?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.0026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:38:25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Who is the Administrative Officer?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/extra-curricular/)
+• [TKRCET Official Page](https://tkrcet.ac.in/diploma/)
+• [TKRCET Official Page](https://tkrcet.ac.in/student-welfare/)
+I'm sorry but I am unable to verify who the administrative officer at TKR College Of Engineering &amp; Technology is.
+📚 **Source Links:**
+• https://tkrcet.ac.in/extra-curricular/
+• https://tkrcet.ac.in/diploma/
+• https://tkrcet.ac.in/student-welfare/
+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>50.0004</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:38:37</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Can you tell me who the HOD of EEE is?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>**Dr. K. Raju** heads the **EEE** department.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.0182</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:39:43</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>What is the contact for Director?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/code-of-conduct/)
+• [TKRCET Official Page](https://tkrcet.ac.in/finance-committe/)
+I don't have direct access to real-time information about specific institutions or their staff, including a director. However, I can suggest some options for you to find the contact information of the director at your institution:
+1. **Check the official website**: Visit the official website of your institution and look for
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/code-of-conduct/
+• https://tkrcet.ac.in/finance-committe/
+</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>53.4973</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:41:09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tell me the fees for 2nd year.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/admissions/admission-procedure/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/time-tables/)
+I don't have that information. The provided text doesn't mention the tuition fees for any particular year, including the 2nd year. If you're looking for specific fee details, I recommend checking with the college's official website or contacting their admissions department directly. They should be able to provide you
+📚 **Source Links:**
+• https://tkrcet.ac.in/admissions/admission-procedure/
+• https://tkrcet.ac.in/autonomous/time-tables/
+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>83.7760</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:41:10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Can you give me information about Identity Cards?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-sections/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/notifications/)
+• [TKRCET Official Page](https://tkrcet.ac.in/student-welfare/)
+Based on the provided sources, here is some information about Identity Cards from TKR College Of Engineering &amp; Technology:
+Identity Cards are issued to all students and staff members of the college. These cards serve as a proof of identity and can be used for various purposes such as accessing college facilities, participating in events
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/library-sections/
+• https://tkrcet.ac.in/autonomous/notifications/
+• https://tkrcet.ac.in/student-welfare/
+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48.6949</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:41:55</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tell me about Placements.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+According to my knowledge, here are some details about placements at TKR Educational Society:
+*   The college has a dedicated placement cell that works closely with top companies to provide job opportunities for its students.
+*   In recent years, the college has seen a significant increase in the number of students placed,
+📚 **Source Links:**
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>42.8300</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:42:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Where is the Playground?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.0030</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:42:13</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Who is in charge of Bus Transport?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>**College Transport:**
+TKRCET provides a fleet of buses connecting all major parts of Hyderabad city to the campus. Transport is safe, reliable, and available for both students and staff.
+**Routes:** Buses operate from Dilshuknagar, LB Nagar, Secunderabad, Uppal, Mehdipatnam, Kukatpally, and other key areas.
+For specific route map and fee details, please visit the Transport Section in the Administrative Block.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.0070</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:43:07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Do you have info on Library Rules?</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-sections/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/digital-library/)
+Yes, we do have information on library rules. You can find the library rules by clicking on the "Library" tab and then selecting the "Rules &amp; Regulations" link.
+Here are some of the key points that you may want to know:
+*   Library hours of operation
+*   Borrowing
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/library-sections/
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/library/digital-library/
+</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>43.8493</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:43:09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Explain College Timings to me.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>**College Timings:**
+🕐 9:40 AM to 4:20 PM (Monday-Saturday)
+**Lunch Break:** 12:40 PM to 1:20 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:44:22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Explain Medical Facilities to me.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+Hello! I'd be happy to explain the medical facilities available at TKR College of Engineering and Technology.
+Unfortunately, I don't have any specific information about the medical facilities provided by the college. However, I can provide some general information that might be helpful.
+Many colleges, including engineering colleges like TK
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>45.4948</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:44:26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>What is the fee structure for 3rd year?</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:44:37</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>What is the fee structure for 3rd year?</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:45:20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>What are the details for Admissions?</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Visit https://tkrcet.ac.in/admissions for admission details and fee structure.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.2879</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:46:15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Who is in charge of NSS?</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>National Service Scheme (NSS)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.0497</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:46:47</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Where is the Playground?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.0155</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:47:44</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Explain Industrial Visits to me.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+Hello Student!
+Industrial Visits are an essential part of a student's educational experience, especially for engineering and technology students like you. An Industrial Visit is a field trip where your college takes you to a real-world industrial setting to learn about the manufacturing process, technologies, and innovations in action.
+The purpose
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/transport/
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>46.3383</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:47:48</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>I want to know about Student Clubs.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>&lt;generator object UltraRAGSystem.__call__ at 0x000001F4CA130580&gt;</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.0442</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>RAG/Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:48:03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Where is the Workshop?</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.0040</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:48:56</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Do you have info on Industrial Visits?</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/time-tables/)
+We do offer Industrial Visits as part of our curriculum.
+Our college has a strong industry-academia partnership, and we organize Industrial Visits for our students to provide them with hands-on experience in the field. These visits are designed to give our students a better understanding of the real-world applications of
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/facilities/transport/
+• https://tkrcet.ac.in/autonomous/time-tables/
+</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>41.0368</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:49:44</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Does the college have a Solar Power?</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+• [Related Resource](https://nlist.inflibnet.ac.in/veresources.php)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/downloads/syllabus-question-papers/)
+I don't see any information about solar power on the provided webpage. However, I can suggest some ways to find out if the college has a solar power system:
+1. Check the college's website for an "About Us" or "Sustainability" section.
+2. Look for a statement on
+📚 **Source Links:**
+• https://tkrcet.ac.in/placement-news/student-placement-details
+• https://nlist.inflibnet.ac.in/veresources.php
+• https://tkrcet.ac.in/library/downloads/syllabus-question-papers/
+</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>42.4733</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:50:28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Who is in charge of Results?</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.in/)
+• [TKRCET Official Page](https://tkrcet.ac.in/examination-committee/)
+According to the information provided, Dr. D. Nageshwar Rao is the Controller of Examinations, which implies that he is in charge of handling and releasing results. However, it would be best to confirm with him directly or check the official notification for the most up-to-date information on
+📚 **Source Links:**
+• https://tkrcet.in/
+• https://tkrcet.ac.in/examination-committee/
+</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>40.2298</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:51:10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Who is in charge of Admissions?</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/admissions/admission-procedure/)
+• [TKRCET Official Page](https://tkrcet.ac.in/extra-curricular/)
+According to the information provided, Dr. D. seems to be the person in charge of admissions, as they are listed under the "Name" column in the Extra Curricular Committee page, along with their designation (which is not explicitly mentioned). However, without further context or clarification, it's difficult
+📚 **Source Links:**
+• https://tkrcet.ac.in/admissions/admission-procedure/
+• https://tkrcet.ac.in/extra-curricular/
+</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>39.7695</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:52:03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Where is the Canteen?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.0040</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:52:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Who manages Sports?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+The Sports in the campus is managed by the "Sports Department" of the college, but I do not have information on who specifically manages it. However, I can suggest that you contact the college administration or the website's "Contact Us" page to inquire about the specific person or department responsible for managing
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>36.6900</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:53:38</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Is Medical Room available?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+I'm happy to help you with your question!
+Unfortunately, I don't have direct access to the facilities and services of TKR College Of Engineering &amp; Technology. However, I can suggest some possible ways for you to find the information you're looking for.
+To confirm if a Medical Room is available at
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>31.5024</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:53:39</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Where is the ECE Department?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:54:16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Where can I find the ECE Department?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/departments/electronics-communication-engineering/)
+• [TKRCET Official Page](https://tkrcet.ac.in/electrical-electronics-engineering/)
+• [TKRCET Official Page](https://tkrcet.ac.in/e-resources/)
+You can find the Electrical and Electronics (ECE) Department at:
+TKR College Of Engineering &amp; Technology
+(You can also check their official website or campus map for more details.)
+📚 **Source Links:**
+• https://tkrcet.ac.in/departments/electronics-communication-engineering/
+• https://tkrcet.ac.in/electrical-electronics-engineering/
+• https://tkrcet.ac.in/e-resources/
+</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>28.2531</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:54:51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Is the Placement Cell open?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/women-cell/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+I'm sorry to inform you that I don't have real-time access to the specific information regarding the current status of the placement cell at TKR College Of Engineering &amp; Technology. However, I can suggest a few options for you to get in touch with them:
+1. **Check their website**: You
+📚 **Source Links:**
+• https://tkrcet.ac.in/women-cell/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>33.5412</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:55:25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Basketball Court open?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+Unfortunately, I don't have real-time access to the specific information about the basketball court at TKR College Of Engineering &amp; Technology. However, I can suggest some possible ways for you to find out if the basketball court is open.
+You can try visiting the official website of TKR College Of Engineering &amp;
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>31.1199</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:55:35</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Explain Canteen Menu to me.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>**College Canteen**
+The college canteen provides hygienic food, snacks, and beverages at subsidized rates. It is a clean and spacious area where students can relax and refuel.
+**Menu:** South Indian, North Indian, Chinese snacks, and beverages.
+**Timings:** Open during college hours (including lunch break).</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.0131</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:55:42</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Can you give me information about NSS?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>National Service Scheme (NSS)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.0527</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:55:52</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>I want to know about College Timings.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>**College Timings:**
+🕐 9:40 AM to 4:20 PM (Monday-Saturday)
+**Lunch Break:** 12:40 PM to 1:20 PM</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:55:59</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Location of ECE Department?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:56:35</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Who manages Scholarships?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/alumni/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+I don't have the specific information on who manages scholarships at TKR College Of Engineering &amp; Technology. However, I can suggest some possible ways to find the answer:
+1. Check the college's official website: You can visit the college's official website and look for a section on scholarships or student support
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/alumni/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>29.4452</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:57:27</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Location of Workshop?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0.0010</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:58:06</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Is Medical Room available?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+I don't have the specific information on whether a medical room is available at TKR College Of Engineering &amp; Technology. However, I can suggest some options for you to find out:
+1. Contact the college administration or the student affairs department directly to inquire about the availability of a medical room.
+2.
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>27.6204</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:58:14</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Do you have info on Bus Transport?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>**College Transport:**
+TKRCET provides a fleet of buses connecting all major parts of Hyderabad city to the campus. Transport is safe, reliable, and available for both students and staff.
+**Routes:** Buses operate from Dilshuknagar, LB Nagar, Secunderabad, Uppal, Mehdipatnam, Kukatpally, and other key areas.
+For specific route map and fee details, please visit the Transport Section in the Administrative Block.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:58:29</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Can you give me information about Hostel Fees?</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.0390</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02-21 21:59:36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>How can I contact the Placement Officer?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+According to the information provided on the website, you can contact the Placement Officer by reaching out to the TKR Educational Society through their official channels. Since the exact contact details of the Placement Officer are not mentioned, here are a few suggestions:
+1. **Check the Staff/Student Login**: You may
+📚 **Source Links:**
+• https://tkrcet.ac.in/placement-news/student-placement-details
+• https://tkrcet.ac.in/placements/
+</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>26.9626</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:00:15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Do we have Library facilities?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/digital-library/)
+• [Related Resource](https://nlist.inflibnet.ac.in/veresources.php)
+Yes, you do have library facilities! You can access the NLIST (National Library and Information Services Network) website which provides a wide range of online resources, including e-books, journals, and other academic materials. Additionally, your college is connected to the INFLIBNET Centre, Gandhinagar
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/digital-library/
+• https://nlist.inflibnet.ac.in/veresources.php
+</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>37.7679</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:00:17</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Where is the Main Gate?</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:00:59</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Who is in charge of Internet Access?</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/departments/electronics-communication-engineering/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+According to the information provided, I don't have any specific details on who is in charge of internet access at TKR College Of Engineering &amp; Technology. However, as a general resource, you can try contacting the college administration or IT department for more information on their internet access policies and procedures.
+📚 **Source Links:**
+• https://tkrcet.ac.in/departments/electronics-communication-engineering/
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>29.2370</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:02:42</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>What is the contact for NCC Officer?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>National Cadet Corps (NCC)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0.0533</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:03:09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>How can I contact the HOD of Mechanical?</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>**Mr. D. Rushi Kumar** heads the **Mechanical** department.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0.0153</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:03:43</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Do we have Conference Room facilities?</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+I'm happy to help you with your question about the conference room facilities at TKR College of Engineering &amp; Technology!
+According to my research, it seems that I don't have access to the most up-to-date information on the college's facilities. However, I can suggest some options for you to find
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>25.4885</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:04:19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Do we have Auditorium facilities?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+According to the information available on the website of TKR College of Engineering and Technology, yes, they do have auditorium facilities.
+Here are the details:
+* They have an Open-Air Auditorium.
+* They also have a Mini-Auditorium.
+Both auditoriums were designed by Bes
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>33.4999</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:04:21</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Do we have Canteen facilities?</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>**College Canteen**
+The college canteen provides hygienic food, snacks, and beverages at subsidized rates. It is a clean and spacious area where students can relax and refuel.
+**Menu:** South Indian, North Indian, Chinese snacks, and beverages.
+**Timings:** Open during college hours (including lunch break).</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0.0010</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:04:31</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Who manages Hostel Fees?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0.0367</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:05:10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Where can I find the Indoor Games Room?</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+I'm sorry to say, but as a helpful assistant, I don't have direct access to the facilities map of TKR College Of Engineering Technology. However, I can suggest a few options for you to find the Indoor Games Room:
+1. **Check the college's official website**: You can visit
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>30.2439</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:05:52</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Explain Placements to me.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+According to the provided information, Placements at TKR Educational Society refer to the process of recruiting students from the institution for jobs or further studies with top companies. It appears that the society has a strong focus on academic excellence and career opportunities for its students.
+While I don't have specific details on the
+📚 **Source Links:**
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>30.1731</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:06:26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tell me about Placements.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+The placements at TKR College are quite impressive!
+According to various sources, including the college's own website and alumni feedback, here are some key highlights about the placements:
+* **High Placement Percentage**: The college has consistently reported high placement percentages in recent years, with many students securing top-tier job offers
+📚 **Source Links:**
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>31.2512</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:06:33</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>How can I contact the HOD of ECE?</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>For **ECE**, the HOD is **Dr. D. Nageshwar Rao**.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:06:42</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Explain NSS to me.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>National Service Scheme (NSS)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0.0379</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:06:50</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Can you tell me who the HOD of MBA is?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>For **MBA**, the HOD is **Dr. K. Gyaneswari**.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0.0010</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:07:37</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Is the Girls Hostel open?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+I'm happy to help, but I don't see a specific question about the girls hostel. However, I can try to answer based on general knowledge.
+Unfortunately, I don't have information about the specific girls hostel you're referring to. If you could provide more context or clarify which institution's girls
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/facilities/transport/
+</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>34.9226</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:08:15</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Does the college have a ATM?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/bank-atm/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+Yes, the college has an ATM machine on campus. It can be found in the Campus Resources section of the website.
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/bank-atm/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>27.3503</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:08:17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>What is the contact for NCC Officer?</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>National Cadet Corps (NCC)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0.0493</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:08:56</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Is there a Conference Room on campus?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+I don't have direct access to the specific facilities of TKR College Of Engineering &amp; Technology. However, I can suggest some possible ways for you to find out if there is a Conference Room on campus.
+You can try visiting the college's official website and looking for information about their facilities and amenities.
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>32.7501</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:10:05</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Who is in charge of College Timings?</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>**College Timings:**
+🕐 9:40 AM to 4:20 PM (Monday-Saturday)
+**Lunch Break:** 12:40 PM to 1:20 PM</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0.0108</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:10:58</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tell me about Alumni Association.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/alumni/)
+• [TKRCET Official Page](https://tkrcet.ac.in/extra-curricular/)
+The Alumni Association of TKR College Of Engineering &amp; Technology is a community of graduates who have shared a common educational experience at the college. The association aims to provide a platform for alumni to connect with each other, stay updated about the college's activities, and give back to the institution.
+Some key features
+📚 **Source Links:**
+• https://tkrcet.ac.in/alumni/
+• https://tkrcet.ac.in/extra-curricular/
+</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>33.8610</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:12:06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Is the Basketball Court open?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+Unfortunately, I don't have the latest information on whether the basketball court is open or not. However, I can suggest some options to find out:
+1. Contact the college administration directly via phone or email.
+2. Check the college's social media pages or website for updates on facilities and opening hours
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>36.8433</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:12:08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Details about HOD of Mechanical?</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>For **Mechanical**, the HOD is **Mr. D. Rushi Kumar**.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0.0091</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:12:43</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>I want to know about NCC.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>National Cadet Corps (NCC)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0.0544</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:13:39</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>How do I get to the Basketball Court?</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+Unfortunately, I don't see any information about a basketball court on the provided pages. However, I can try to help you find it.
+According to the "Sports" page (https://tkrcet.ac.in/facilities/sports/), the college has a playground with facilities for cricket,
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>28.9081</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:14:09</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Who is in charge of Events?</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/2024-events/)
+• [TKRCET Official Page](https://tkrcet.ac.in/2022-2023-events/)
+Dr. K. Suresh Kumar is the Head of Department for Civil Engineering and also in charge of all events at TKR College Of Engineering &amp; Technology.
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/2024-events/
+• https://tkrcet.ac.in/2022-2023-events/
+</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>29.0999</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:14:11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Can you tell me who the HOD of IT is?</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The HOD of **IT** is **Dr. R. Muruanantham**.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.0040</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:14:58</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Can you give me information about Convocation?</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+Unfortunately, I don't see any information about Convocation in the text. However, I can tell you that Convocation is a ceremony held to mark the completion of a degree or qualification program at a university or college.
+If you're looking for information about Convocation at TKR College Of Engineering &amp;
+📚 **Source Links:**
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>34.4480</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:16:42</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Is the Board Room open?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+I'm happy to help you, but I don't have real-time information about the status of the Board Room at TKR College Of Engineering &amp; Technology. However, I can suggest some options to find out if it's open:
+1. Contact the college administration or the department where the Board Room is
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>35.8791</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:16:59</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>What is the fee structure for 2nd year?</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:17:13</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Does the college have a Hostel?</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>College Canteen</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0.0969</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:17:59</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tell me about Internships.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/admissions/admission-procedure/)
+I'm happy to help you with your question!
+According to the information available on the website of TKR College of Engineering and Technology, it appears that they have a dedicated page for "Internships" (although I couldn't find an exact match). However, I can tell you about some relevant pages
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/admissions/admission-procedure/
+</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>32.4114</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:19:12</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Is Hostel available?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0.7246</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:19:17</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Who is the Vice Principal?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>**Dr. A. Suresh Rao (also HoD of CSE &amp; Dean Academics)** is the Vice Principal of our college.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0.4164</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:19:22</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fee details for 2nd year student?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/time-tables/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-sections/)
+• [TKRCET Official Page](https://tkrcet.ac.in/exam-branch/student-list/)
+To find the fee details for a 2nd year student, I would recommend checking with the college administration or the student's department. However, based on the provided links, here are some possible sources where you may be able to find the information:
+1. **Student-list webpage**: You can check
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/time-tables/
+• https://tkrcet.ac.in/library/library-sections/
+• https://tkrcet.ac.in/exam-branch/student-list/
+</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>33.0785</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:19:59</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Is there a Smart Classroom on campus?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/downloads/syllabus-question-papers/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+No, I don't have any information about the presence of a Smart Classroom on campus. However, I can suggest some ways for you to find out if there is one:
+1. Visit the official website of TKR College of Engineering and Technology ([www.tkrcet.ac.in](http://www
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/downloads/syllabus-question-papers/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>32.7178</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:20:34</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tell me about Events.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/2024-events/)
+• [TKRCET Official Page](https://tkrcet.ac.in/2022-2023-events/)
+At TKR College Of Engineering &amp; Technology, there are various exciting events happening throughout the year. Here's a brief overview of some of the notable events:
+**2022-2023 Events**
+Unfortunately, I couldn't find any information on specific events for 2022-2023.
+**202
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/2024-events/
+• https://tkrcet.ac.in/2022-2023-events/
+</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>31.3430</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:21:19</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Does the college have a Water Purifier?</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+I don't see any information about water purifiers on the provided sources. However, I can suggest some possible ways to find out if the college has a water purifier.
+You could try contacting the college administration or student affairs department directly and ask them about the availability of a water purifier on campus
+📚 **Source Links:**
+• https://tkrcet.ac.in/placement-news/student-placement-details
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/facilities/transport/
+</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>31.0927</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:22:12</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tell me the fees for 3rd year.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/time-tables/)
+• [TKRCET Official Page](https://tkrcet.ac.in/admissions/admission-procedure/)
+I don't have any information about the specific fees for a 3rd year student at TKR College Of Engineering &amp; Technology. However, I can suggest that you check the college's official website or contact their admissions department directly to get the most up-to-date and accurate information about fees for the current
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/time-tables/
+• https://tkrcet.ac.in/admissions/admission-procedure/
+</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>33.5535</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:22:56</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>How do I get to the ECE Department?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/departments/electronics-communication-engineering/)
+• [TKRCET Official Page](https://tkrcet.ac.in/electrical-electronics-engineering/)
+• [TKRCET Official Page](https://tkrcet.ac.in/finance-committe/)
+To get to the ECE (Electrical and Computer Engineering) Department, you can follow these steps:
+1. From the main campus of TKR College Of Engineering &amp; Technology, head towards the Administration Building.
+2. Once inside the building, look for the sign that says "Departments" or
+📚 **Source Links:**
+• https://tkrcet.ac.in/departments/electronics-communication-engineering/
+• https://tkrcet.ac.in/electrical-electronics-engineering/
+• https://tkrcet.ac.in/finance-committe/
+</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>41.5103</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:23:14</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Who manages Student Clubs?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>&lt;generator object UltraRAGSystem.__call__ at 0x000001F4ED2CEA40&gt;</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0.0764</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>RAG/Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:23:58</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>How can I contact the Director?</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/contact-us/)
+• [TKRCET Official Page](https://tkrcet.ac.in/extra-curricular/)
+I don't have a specific contact information for the Director, but you can try reaching out to the following people:
+* Vice-Principal Dr. A. Suresh Rao: He may be able to direct your inquiry to the appropriate person or provide guidance on how to contact the Director.
+* Principal
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/contact-us/
+• https://tkrcet.ac.in/extra-curricular/
+</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>29.3737</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:24:38</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>What is the contact for Vice Principal?</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>The Vice Principal is **Dr. A. Suresh Rao (also HoD of CSE &amp; Dean Academics)**.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:25:19</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>What are the details for Sports?</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+According to the provided information, here are the details for Sports at TKR College of Engineering and Technology:
+* The campus has a 5-acre lush green playground with floodlights for cricket, football, and other outdoor sports.
+* The playground is designed by Besure.Today.
+If you need more information
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/events-2/
+</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>27.6915</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:28:09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Do we have Solar Power facilities?</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/electrical-electronics-engineering/)
+Yes, TKRCET has installed solar power facilities to promote sustainability and reduce carbon footprint on campus. The college aims to harness renewable energy and contribute to a greener environment.
+Source: TKRCET website (same link as before)
+📚 **Source Links:**
+• https://tkrcet.ac.in/electrical-electronics-engineering/
+</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>39.8998</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:28:09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Can you give me information about Convocation?</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+A milestone event!
+Convocation is a significant ceremony held at many educational institutions, including colleges and universities, to mark the completion of a student's academic program. Here are some key details about convocation:
+**What happens during convocation?**
+During convocation, students who have completed their degree or
+📚 **Source Links:**
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>61.3178</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:28:58</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Can you give me information about Dress Code?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/code-of-conduct/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+Here is the response:
+Dear Student,
+Thank you for reaching out to our Complaint Cell. We're happy to assist you with any concerns or questions you may have.
+Regarding your question, our institution follows a dress code policy that aims to promote a professional and respectful atmosphere on campus. The dress code guidelines
+📚 **Source Links:**
+• https://tkrcet.ac.in/code-of-conduct/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>32.5855</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:29:32</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Where can I find the Placement Cell?</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/women-cell/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+You can find the Placement Cell at:
+https://tkrcet.ac.in/placement-cell/
+Alternatively, you can also check with the college administration or visit the campus to get the exact location of the Placement Cell.
+📚 **Source Links:**
+• https://tkrcet.ac.in/women-cell/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>31.7573</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:29:37</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Location of Parking Area?</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0.0050</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:29:48</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>What are the details for Student Clubs?</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>&lt;generator object UltraRAGSystem.__call__ at 0x000001F4ED2CE650&gt;</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0.0165</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>RAG/Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:29:58</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Can you tell me who the HOD of ECE is?</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>The HOD of **ECE** is **Dr. D. Nageshwar Rao**.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0.0052</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:30:14</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Location of CSE Department?</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0.0155</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:30:23</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>What is the contact for HOD of IT?</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>**Dr. R. Muruanantham** heads the **IT** department.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0.0032</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:31:34</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Explain Medical Facilities to me.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+Hello!
+As a student of TKR College Of Engineering &amp; Technology, you may be wondering about the medical facilities available on campus. Unfortunately, I don't have specific information about the medical facilities at your college, as my training data doesn't contain details about this particular institution.
+However, I can tell
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>63.3166</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:31:35</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Who is in charge of Anti-Ragging?</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/notifications/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+According to the information available on the website, there isn't a specific person mentioned as being directly in charge of Anti-Ragging. However, it does mention that there is a "Grievance Redressal committee" which suggests that there are measures in place to address and resolve grievances related
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/notifications/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>43.4048</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:32:07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>What is the contact for Lab Assistant?</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/virtual-labs/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+I don't have that information. You can try contacting the college administration or laboratory directly to inquire about the contact details of the lab assistant.
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/virtual-labs/
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>27.3787</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:32:49</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Does the college have a Auditorium?</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+According to the information provided, yes, the TKR College of Engineering and Technology has an Open-Air Auditorium. However, I couldn't find any specific mention of a Mini-Auditorium on their website.
+If you're looking for more information about the college's facilities or want to confirm
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>30.4409</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:33:27</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>What is the contact for Librarian?</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/digital-library/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-sections/)
+The contact information for the Librarian at TKRC EAMCET college is not provided. However, you can try contacting the college administration or library department directly to inquire about the librarian's contact details. Alternatively, you can check the college's official website or social media channels for any updates on the
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/digital-library/
+• https://tkrcet.ac.in/library/library-sections/
+</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>30.6538</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:35:36</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Where can I find the Chemistry Lab?</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/virtual-labs/)
+• [TKRCET Official Page](https://tkrcet.ac.in/naac-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-committee/)
+I'd be happy to help you find the Chemistry Lab at TKR College of Engineering and Technology.
+Unfortunately, I couldn't find any information on the exact location of the Chemistry Lab on the provided websites. However, I suggest checking with the college administration or the student affairs department for more information on the
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/virtual-labs/
+• https://tkrcet.ac.in/naac-2/
+• https://tkrcet.ac.in/library/library-committee/
+</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>27.3309</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:35:39</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Where is the Reception?</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>**TKRCET Location:**
+📍 Meerpet, Hyderabad - 500097, Telangana
+**Established:** 2002
+**Affiliation:** JNTUH (Jawaharlal Nehru Technological University Hyderabad)
+**Status:** Autonomous (UGC confirmed)
+**Campus Size:** 20 acres</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0.0061</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:36:01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>How can I contact the Exam Branch Incharge?</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Exam schedules are announced by the Examination Branch. Please check the college notice board, website, or contact your department for specific dates.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0.0970</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:36:06</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>How do I get to the Exam Branch?</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Exam schedules are announced by the Examination Branch. Please check the college notice board, website, or contact your department for specific dates.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0.0466</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:36:52</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Where can I find the Physics Lab?</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/virtual-labs/)
+• [TKRCET Official Page](https://tkrcet.ac.in/nirf/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-committee/)
+Unfortunately, I don't have the exact location of the Physics Lab at TKR College Of Engineering &amp; Technology. However, I can suggest a few options to help you find it:
+1. **Check the college website**: You can visit the official website of TKR College Of Engineering &amp; Technology and search
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/virtual-labs/
+• https://tkrcet.ac.in/nirf/
+• https://tkrcet.ac.in/library/library-committee/
+</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>27.1761</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:38:02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Is there a Digital Library on campus?</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/digital-library/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-sections/)
+Yes, there is a Digital Library on campus. In fact, the college has two resources related to libraries that you mentioned:
+1. A Digital Library (also referred to as a "Digital Resource" or "Online Resource"): This would be an online collection of digital materials such as e-books, articles
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/digital-library/
+• https://tkrcet.ac.in/library/library-sections/
+</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>28.2037</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:38:12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Who is the HOD of Mechanical?</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>For **Mechanical**, the HOD is **Mr. D. Rushi Kumar**.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.0172</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:38:52</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Where can I find the Parking Area?</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+I'm happy to help you with your question!
+However, I couldn't find any information about a parking area on the provided webpage of TKR College Of Engineering &amp; Technology. It seems that the webpage only provides information about transportation (bus routes and schedules).
+If you're looking for the parking area,
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+• https://tkrcet.ac.in/facilities/transport/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>29.3110</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:38:54</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>What is the contact for HOD of EEE?</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>For **EEE**, the HOD is **Dr. K. Raju**.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:39:06</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>I want to know about Bus Transport.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>**College Transport:**
+TKRCET provides a fleet of buses connecting all major parts of Hyderabad city to the campus. Transport is safe, reliable, and available for both students and staff.
+**Routes:** Buses operate from Dilshuknagar, LB Nagar, Secunderabad, Uppal, Mehdipatnam, Kukatpally, and other key areas.
+For specific route map and fee details, please visit the Transport Section in the Administrative Block.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.0055</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:39:33</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Can you give me information about College Timings?</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>**College Timings:**
+🕐 9:40 AM to 4:20 PM (Monday-Saturday)
+**Lunch Break:** 12:40 PM to 1:20 PM</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.0056</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:40:07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>I want to know about Library Rules.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/library-sections/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/digital-library/)
+As part of the TKR College Of Engineering &amp; Technology, here are some general library rules that students and staff should be aware of:
+**Library Rules:**
+1. **Registration**: All students and staff must register themselves with the library before borrowing any materials.
+2. **Identification**: A valid student
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/library-sections/
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/library/digital-library/
+</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>30.2721</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:41:12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Where can I find the Indoor Games Room?</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+I'm sorry but we do not have an indoor games room. However, you can make use of our open-air auditorium which is fully equipped with modern amenities and well-maintained to provide a serene environment for students to hold various events, including sports activities, workshops, lectures and more.
+Alternatively
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>62.4312</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:41:13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Do we have Wi-Fi facilities?</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/wp-content/uploads/2019/02/TKRCET_Routemap.pdf)
+• [TKRCET Official Page](https://tkrcet.ac.in/departments/electronics-communication-engineering/)
+According to the information provided, I couldn't find any mention of Wi-Fi facilities specifically. However, I can suggest some ways for you to find out if TKR College Of Engineering &amp; Technology has Wi-Fi facilities:
+1. Check their official website: You can visit the college's official website and look
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/wp-content/uploads/2019/02/TKRCET_Routemap.pdf
+• https://tkrcet.ac.in/departments/electronics-communication-engineering/
+</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>39.7309</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:41:47</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Do we have Smart Classroom facilities?</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/library/downloads/syllabus-question-papers/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+After conducting a thorough search on the provided links, I was unable to find any information on whether TKR College of Engineering and Technology has Smart Classroom facilities or not.
+However, I can suggest some possible ways for you to find out:
+1. Visit the college's official website: You can try searching
+📚 **Source Links:**
+• https://tkrcet.ac.in/library/downloads/syllabus-question-papers/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>31.6044</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:41:53</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>How can I contact the HOD of CSE?x</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>For **CSE**, the HOD is **Dr. A. Suresh Rao**.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:42:43</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Can you give me information about Events?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/2024-events/)
+• [TKRCET Official Page](https://tkrcet.ac.in/2022-2023-events/)
+I can try to help you with that!
+Unfortunately, I couldn't find any information about "Events" on the website of TKR College Of Engineering &amp; Technology. However, I did find some archived pages for previous events:
+* 2024 Events: https://tkrcet.ac.in/202
+📚 **Source Links:**
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/2024-events/
+• https://tkrcet.ac.in/2022-2023-events/
+</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>29.5434</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:42:45</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Who is in charge of Hostel Fees?</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>**Fee Structure (Approximate):**
+• **B.Tech:** Tuition fee for B.Tech is approximately ₹85,000 - ₹1,00,000 per year (depending on the quota and branch).
+• **M.Tech:** Tuition fee for M.Tech is approximately ₹57,000 per year.
+• **MBA:** Tuition fee for MBA is approximately ₹54,000 per year.
+• **Hostel:** Hostel fee is around ₹70,000 - ₹80,000 per year (including mess).
+• **Transport:** Transport fee varies by distance, ranging from ₹18,000 to ₹35,000 per year.
+_Fees are subject to change as per government regulations. Contact accounts department for exact figures._</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0.0815</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:42:47</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Who manages NSS?</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>National Service Scheme (NSS)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0.0549</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:43:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Details about Admission Incharge?</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Visit https://tkrcet.ac.in/admissions for admission details and fee structure.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0.0682</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:43:38</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Can you give me information about Industrial Visits?</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+• [TKRCET Official Page](https://tkrcet.ac.in/events-2/)
+• [TKRCET Official Page](https://tkrcet.ac.in/e-resources/)
+We organize industrial visits to various companies and industries in order to provide our students with hands-on experience and exposure to the real-world applications of their studies.
+Our Industrial Visit Programme is designed to:
+*   Provide students with a practical understanding of the concepts learned in the classroom
+*   Offer opportunities for students
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/transport/
+• https://tkrcet.ac.in/events-2/
+• https://tkrcet.ac.in/e-resources/
+</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>28.8466</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:43:44</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>What is the contact for Transport Incharge?</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>**College Transport:**
+TKRCET provides a fleet of buses connecting all major parts of Hyderabad city to the campus. Transport is safe, reliable, and available for both students and staff.
+**Routes:** Buses operate from Dilshuknagar, LB Nagar, Secunderabad, Uppal, Mehdipatnam, Kukatpally, and other key areas.
+For specific route map and fee details, please visit the Transport Section in the Administrative Block.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0.0075</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:44:32</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>How do I get to the Indoor Games Room?</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/open-air-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+I'm happy to help you! However, I don't see an "Indoor Games Room" mentioned on the website. But I can suggest some possible options:
+1. Check the campus map or layout: You can try searching for a map of the campus online or ask someone in the administration office
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/open-air-auditorium/
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/facilities/sports/
+</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>29.4423</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:45:07</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Do we have Stationery Shop facilities?</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+Unfortunately, I don't have the specific information about a stationery shop facility at TKR College Of Engineering &amp; Technology. However, I can suggest some possible ways to find out:
+1. Check the college website: You can visit the official website of TKR College Of Engineering &amp; Technology and look for
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+• https://tkrcet.ac.in/facilities/transport/
+</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>33.0551</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:45:10</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>How can I contact the Exam Branch Incharge?</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Exam schedules are announced by the Examination Branch. Please check the college notice board, website, or contact your department for specific dates.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0.0747</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:46:01</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Do we have Stationery Shop facilities?</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/mini-auditorium/)
+• [TKRCET Official Page](https://tkrcet.ac.in/library/introduction/layout-floor-plan/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/transport/)
+I'm happy to help you with your question!
+According to the TKR College Of Engineering &amp; Technology website, I was unable to find any information regarding a stationery shop. However, I can suggest that you check with the college administration or student union to inquire about their facilities and services.
+If you
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/mini-auditorium/
+• https://tkrcet.ac.in/library/introduction/layout-floor-plan/
+• https://tkrcet.ac.in/facilities/transport/
+</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>28.8821</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:46:37</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>What is the contact for Lab Assistant?</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/virtual-labs/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/complaint-cell/)
+I don't have the specific contact information for a Lab Assistant at TKR College of Engineering and Technology. However, I can suggest some options to help you find the information:
+1. Check the college website: You can visit the official website of TKR College of Engineering and Technology and look for the
+📚 **Source Links:**
+• https://tkrcet.ac.in/facilities/virtual-labs/
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/complaint-cell/
+</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>34.6993</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:51:50</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>on which year tkr college is established</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>The **TKR Educational Society** manages the following institutions:
+1. TKR College of Engineering and Technology (TKRCET) - Autonomous
+2. Teegala Krishna Reddy Engineering College (TKREC)
+3. TKR College of Pharmacy (TKRCOP)
+4. TKR Institute of Management and Science (TKRIMS)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0.4048</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:52:18</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>what are the different branches there in tkr</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>**Courses Offered:**
+🎓 **B.Tech:** CSE, CSE-AIML, CSE-DS, ECE, EEE, IT, Mechanical, Civil
+🎓 **M.Tech/MBA:** M.Tech in CSE, M.Tech in Power Electronics, MBA</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0.0040</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:53:24</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Is this college autonomous or affiliated?</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/internal-marks/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+The answer is that TKR College of Engineering and Technology (TKRCET) is affiliated, not autonomous. According to the information provided, it has its own academic regulations and placement news section, but the main website seems to be a page not found error.
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/autonomous/internal-marks/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>45.3168</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:54:01</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>What is the intake capacity of CSE?</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/cse-allied-ds/)
+• [TKRCET Official Page](https://tkrcet.ac.in/artificial-intelligence-and-machine-learning-allied-with-cse/)
+• [TKRCET Official Page](https://tkrcet.ac.in/ncc/)
+I don't have that information. However, I can suggest some possible ways to find out the intake capacity of CSE at TKR College Of Engineering &amp; Technology.
+You can check the official website of TKR College Of Engineering &amp; Technology ([https://tkrcet.ac.in/](https://tk
+📚 **Source Links:**
+• https://tkrcet.ac.in/cse-allied-ds/
+• https://tkrcet.ac.in/artificial-intelligence-and-machine-learning-allied-with-cse/
+• https://tkrcet.ac.in/ncc/
+</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>35.1114</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:54:34</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>What electives are offered for final year students?</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>30.0794</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:55:19</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Which department has the highest placements?</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/placements/)
+• [TKRCET Official Page](https://tkrcet.ac.in/placement-news/student-placement-details)
+• [TKRCET Official Page](https://tkrcet.ac.in/events/nss/)
+I don't have that information. The provided text only mentions the overall placement statistics for TKR College Of Engineering &amp; Technology, but it doesn't specify which department has the highest placements. However, I can suggest checking the college's official website or contacting them directly to get more detailed information on department-wise
+📚 **Source Links:**
+• https://tkrcet.ac.in/placements/
+• https://tkrcet.ac.in/placement-news/student-placement-details
+• https://tkrcet.ac.in/events/nss/
+</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>41.6542</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:55:21</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>What is the NAAC grade of the college?</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>A+ Grade</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0.0834</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:55:39</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>What companies visit the campus for placements?</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>College Canteen</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0.0622</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:55:50</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>What is the average package for CSE students?</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Summary (526 students found):
+• Placed students: 131 out of 526
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.04
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 526
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [Placement Cell](https://tkrcet.ac.in/placement/)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0.4040</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:56:26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Is attendance mandatory?</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>No students found matching your criteria.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>23.9487</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:56:27</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>who is the secretary of tkr</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>The Secretary is **Dr. T. Harinath Reddy**.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0.0040</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:57:17</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>how training will be going on</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/autonomous/academic-regulations/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/sports/)
+• [TKRCET Official Page](https://tkrcet.ac.in/examination-committee/)
+According to the information available on the website of TKR College of Engineering and Technology, the college offers various training programs for students. Here are some ways in which training is conducted at the college:
+1. **Lab Training**: The college has well-equipped laboratories for each branch, where students can practice and
+📚 **Source Links:**
+• https://tkrcet.ac.in/autonomous/academic-regulations/
+• https://tkrcet.ac.in/facilities/sports/
+• https://tkrcet.ac.in/examination-committee/
+</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>44.4753</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:57:47</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>highest packapge student name in 2025</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Summary (50 students found):
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [TKRCET Home](https://tkrcet.ac.in/)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>28.8875</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-02-21 22:58:01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>can u list top cgpa students of csd in 2025</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>No students found matching your criteria.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>10.9586</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>6591b71e-7c42-4420-99d6-5d1d97081e81</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:09:03</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Hello! I'm your TKRCET College Buddy! 😊 How can I help you today?</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>76c6b3fa-a5c3-4590-a4f2-d62579de1447</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Instant Response</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:11:47</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>how many students are there in cse</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/artificial-intelligence-and-machine-learning-allied-with-cse/)
+• [TKRCET Official Page](https://tkrcet.ac.in/exam-branch/student-list/)
+• [TKRCET Official Page](https://tkrcet.ac.in/cse-allied-ds/)
+You're looking for some info on the CSE department at TKRCET, eh? Well, let me see what I can find out for you!
+From what I know, **TKRCET has a total of 1648 students**, but I'm not sure if that includes all departments, including CSE. However, based on my research, here are the details about the student population in the CSE department:
+* Total number of students in CSE: Not explicitly mentioned in the provided sources, but according to their website, they have a total of **250+ students** studying under the CSE department.
+* Breakdown of students by semester:
+ + 1st Sem: 70+
+ + 2nd Sem: 80+
+ + 3rd Sem: 90+
+ + 4th Sem: 100+
+ + 5th Sem: 120+
+ + 6th Sem: 150+
+Keep in mind that these numbers might not be up-to-date or exact, as the college's website seems to have some issues with their page titles!
+If you're looking for more information about CSE programs or admission process at TKRCET, I'd recommend checking out their official website (tkrcet.ac.in) or visiting the CSE department directly. They should be able to provide you with the most accurate and up-to-date info.
+How's that? Any other questions or concerns?
+📚 **Source Links:**
+• https://tkrcet.ac.in/artificial-intelligence-and-machine-learning-allied-with-cse/
+• https://tkrcet.ac.in/exam-branch/student-list/
+• https://tkrcet.ac.in/cse-allied-ds/
+</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>137.5328</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>76c6b3fa-a5c3-4590-a4f2-d62579de1447</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>how many students are placed from cse in 2025</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Summary (131 students found):
+• Placed students: 131 out of 131
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.88
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 131
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [Placement Cell](https://tkrcet.ac.in/placement/)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1.1608</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1493965e-5a08-422c-b894-82fdd0d330be</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:32:39</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>how many students are there in cse</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/artificial-intelligence-and-machine-learning-allied-with-cse/)
+• [TKRCET Official Page](https://tkrcet.ac.in/exam-branch/student-list/)
+• [TKRCET Official Page](https://tkrcet.ac.in/cse-allied-ds/)
+Hey there, future CSE student! I'm stoked to help you with any questions you have about TKRCET. So, you want to know how many students are there in the Computer Science and Engineering (CSE) department?
+From my knowledge, **TKR College Of Engineering &amp; Technology** has a total of **1648** students across all departments, including CSE.
+However, I couldn't find an exact figure for just CSE. But don't worry, I can guide you to the right resource!
+You can check the official website of TKRCET ([www.tkrcet.ac.in](http://www.tkrcet.ac.in)) and visit the "Student List" page (which is designed by www.Besure.Today). Unfortunately, it seems like that page isn't working properly as mentioned in your question.
+But you can try looking for the CSE student list on the website's "Exams" or "Departments" section. Sometimes, these links might be available, and you can get an idea of how many students are enrolled in CSE.
+Alternatively, I recommend reaching out to the **Dean Academics** (Dr. A. Suresh Rao) or the **HoD of CSE &amp; Dean Academics** (also Dr. A. Suresh Rao) directly via email or phone. They might be able to provide you with the most up-to-date information on the number of students in CSE.
+Keep me posted if you need any more help, and don't hesitate to ask!
+📚 **Source Links:**
+• https://tkrcet.ac.in/artificial-intelligence-and-machine-learning-allied-with-cse/
+• https://tkrcet.ac.in/exam-branch/student-list/
+• https://tkrcet.ac.in/cse-allied-ds/
+</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>107.8834</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1493965e-5a08-422c-b894-82fdd0d330be</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:26:18</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>COURSES?</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Courses Offered:**
+🎓 **B.Tech:** CSE, CSE-AIML, CSE-DS, ECE, EEE, IT, Mechanical, Civil
+🎓 **M.Tech/MBA:** M.Tech in CSE, M.Tech in Power Electronics, MBA
+📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>0.0487</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>b9960c8d-236b-46f2-acbc-0a269288a5c5</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:31:33</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>FEE DETAILS?</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/finance-committe/)
+• [TKRCET Official Page](https://tkrcet.ac.in/mandatory-disclosures/)
+• [TKRCET Official Page](https://tkrcet.ac.in/facilities/bank-atm/)
+Hey there, future engineer! I'm super glad you reached out to me about TKRCET. Don't worry, I've got all the info you need.
+So, you wanna know the fee details? Well, let me give you a quick rundown:
+* **Tuition Fees**: The tuition fees for TKRCET vary depending on the branch and category of admission. You can check the official website for the most up-to-date fees structure.
+* **Other Fees**: There are additional fees for things like hostel, library, and other facilities. These fees are usually separate from the tuition fees.
+Here's a rough idea of what you might expect to pay:
+* **First Year Tuition Fees**:
+ + General Category: around ₹1.5 lakh per annum
+ + SC/ST/OBC Category: around ₹1.2 lakh per annum
+ + BC Category: around ₹1.4 lakh per annum
+* **Other Fees**:
+ + Hostel fees (if applicable): around ₹50,000 - ₹70,000 per annum
+ + Library fees: around ₹5,000 - ₹10,000 per annum
+Keep in mind that these are just rough estimates and might not include additional fees like transportation or other miscellaneous expenses.
+Now, if you want to get the exact fee details, I'd recommend checking out the official TKRCET website (you know, [https://tkrcet.ac.in/](https://tkrcet.ac.in/)). They usually have a section dedicated to tuition fees and other charges. You can also contact our finance department directly for more information.
+Hope that helps! Let me know if you've got any other questions or need further clarification.
+📚 **Source Links:**
+• https://tkrcet.ac.in/finance-committe/
+• https://tkrcet.ac.in/mandatory-disclosures/
+• https://tkrcet.ac.in/facilities/bank-atm/
+</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>142.9172</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>b9960c8d-236b-46f2-acbc-0a269288a5c5</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:44:51</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>WHO IS PAVANSAI</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Official Page](https://tkrcet.ac.in/press-media-coverage/)
+• [TKRCET Official Page](https://tkrcet.ac.in/iqac-2/)
+• [TKRCET Official Page](https://tkrcet.in/)
+Here's what I found:
+• Title: Press – Media Coverage – TKR College Of Engineering &amp; Technology
+Source: https://tkrcet.ac.in/press-media-coverage/
+EAMCET CODE : TKRC
+Staff/Student Login
+|
+NIRF
+|
+ARIIA
+|
+IQAC
+|
+AQAR
+|
+NAAC
+|
+Alumni
+|
+Library
+New Student Registration Link
+Admission 2025-26
+Press – Media Coverage
+Home
+Press – Media Coverage
+76th Republic Day 2025 News
+View
+The college community mourns the Pahalgam tragedy(22April25), offering heartfelt condolences and deepest sympathies to the bereaved families. View
+23rd Annual Day Celebrations
+View
+76th Republic Day 2025 News
+View
+Recruitment Notification 30 DEC 2024
+View
+Anti Drug awareness programme 09 Aug 24
+View
+Campus Resources
+Student Degree Verification
+New Student Registration
+Income Declaration Form (2024-25)
+NCC
+NSS
+SOP
+Achievements
+Good Governance Document
+Strategic Plan &amp; Program Development Document
+Research Policy Document
+Ombudsperson
+Route Map
+Virtual Tour 360
+Service Rules
+Online Grievance Cell
+B Category / Management Application Form
+Feedbac
+• Title: iqac – TKR College Of Engineering &amp; Technology
+Source: https://tkrcet.ac.in/iqac-2/
+EAMCET CODE : TKRC
+Staff/Student Login
+|
+NIRF
+|
+ARIIA
+|
+IQAC
+|
+AQAR
+|
+NAAC
+|
+Alumni
+|
+Library
+New Student Registration Link
+Admission 2025-26
+IQAC
+Home
+IQAC
+CSE-IQAC-2025-2026
+View
+CSE-IQAC-2024-2025
+View
+CSE-IQAC-2023-2024
+View
+CSE-IQAC-2022-2023
+View
+CSE-IQAC-2021-2022
+View
+Campus Resources
+Student Degree Verification
+New Student Registration
+Income Declaration Form (2024-25)
+NCC
+NSS
+SOP
+Achievements
+Good Governance Document
+Strategic Plan &amp; Program Development Document
+Research Policy Document
+Ombudsperson
+Route Map
+Virtual Tour 360
+Service Rules
+Online Grievance Cell
+B Category / Management Application Form
+Feedback(s)
+Mandatory Disclosures
+Code-of-Conduct
+Home
+TKR Campus
+TKR Educational Society was established in 2001, it is reputedly academic oriented. Sri. Teegala Krishna Reddy, the former Mayor of Hyderabad, Ex-MLA Maheshwaram and leader of masses is the Chairman of the society. A native
+• Title: TKRES Teegala Krishna Reddy Education Society
+Source: https://tkrcet.in/
+With the Help &amp; Support of A. Pradeep, (Additional Controller of Examinations - TKRCET)
+Designer, Developer &amp; Maintenance - Mr. A. Srinivas Reddy (TKREC)
+📚 **Source Links:**
+• https://tkrcet.ac.in/press-media-coverage/
+• https://tkrcet.ac.in/iqac-2/
+• https://tkrcet.in/
+</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>713.6832</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>b9960c8d-236b-46f2-acbc-0a269288a5c5</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>

--- a/logs/response_log.xlsx
+++ b/logs/response_log.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,41 +452,11 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval Confidence (%)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Faithfulness</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Answer Relevance</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-Validation (SQL vs. RAG)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Link Validity</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-27 15:02:43</t>
+          <t>2026-03-03 01:15:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,21 +468,7 @@
         <is>
           <t xml:space="preserve">📌 **Quick Links:**
 • [IT Department](https://tkrcet.ac.in/information-technology/)
-Hey there, future TKRCETian! I'm stoked to be your friendly College Buddy. Don't worry about those typos or unclear questions - we'll get everything sorted out.
-So, you want to know about attendance? Well, let me break it down for you:
-**Attendance Criteria:**
-* Attendance is calculated per subject.
-* The minimum requirement is **75% attendance**, as per JNTUH norms. This means if you miss a class, you need to make up for it by attending the next one.
-Here's a simple way to think about it:
-* If you attend all your classes for a particular subject, that's 100%.
-* If you miss one class but attend the next two, that's 80% (2/3).
-* And so on...
-**Why is attendance important?**
-* It helps you keep up with the coursework and assignments.
-* It shows your commitment to learning and participating in classes.
-* Good attendance can also improve your overall performance in exams.
-Now, I know what you're thinking: "What if I miss a class due to personal reasons?" Don't worry, we've got that covered too! If you need to take a leave, just head to the **College Office** and submit a leave application. They'll help you sort it out.
-Hope this helps, mate! Do you have any more questions about attendance or anything else?
+The attendance criteria for TKRCET is 75% attendance per subject, as per JNTUH norms.
 📚 **Source Links:**
 • [IT Department](https://tkrcet.ac.in/information-technology/)
 </t>
@@ -519,48 +476,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>90.3380</t>
+          <t>25.7916</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>a2c078d8-96ec-46fe-b791-aefa7d1ee045</t>
+          <t>ca34c5e5-3e95-460f-9fab-beedf10d6982</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-27 15:02:48</t>
+          <t>2026-03-03 01:16:15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,56 +503,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A+ Grade
-📌 **Quick Links:**
+          <t xml:space="preserve">📌 **Quick Links:**
 • [NAAC](https://tkrcet.ac.in/naac-2/)
+The NAAC grade of the college is not mentioned in the provided context.
+📚 **Source Links:**
+• [NAAC](https://tkrcet.ac.in/naac-2/)
 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0215</t>
+          <t>19.9354</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>bfa19142-509f-474c-afd4-eafb69a78e7d</t>
+          <t>ff609b78-3f52-433b-9e12-0ace0fb37ee0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
         </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-27 15:03:47</t>
+          <t>2026-03-03 01:16:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,17 +542,11 @@
         <is>
           <t xml:space="preserve">📌 **Quick Links:**
 • [Placements](https://tkrcet.ac.in/placements/)
-Hey there! I'm your friendly TKRCET College Buddy. I'm super excited to help you with all your queries about our amazing college!
-Firstly, let's talk about the placement stats. We're really proud of what we've achieved here at TKRCET. Here are some key numbers:
-* **Total Placed Students:** 351 (as of my last update)
-* **Placement Rate:** 21% (which is pretty impressive if I do say so myself!)
-* **Top Recruiters:**
- + Savantis: 56 students
- + Ncr Atleos: 38 students
- + Dexterity: 35 students
-These numbers are a testament to our Training &amp; Placement Cell's hard work in connecting us with top companies. Our cell focuses on providing continuous student training, company tie-ups, and mock interviews to ensure we're all ready for the real world.
-If you want to know more about our placement process or would like to check out our current job openings, I recommend visiting our college website or contacting our Training &amp; Placement Cell directly. They'll be able to give you the most up-to-date info!
-How's that? Do you have any other questions about TKRCET or placements?
+Hello! I'm your TKRCET College Buddy. 
+Here's the placement statistics:
+- Total Students: 1648
+- Placed Students: 351 (Rate: 21%)
+- Top Recruiters: Savantis (56), Ncr Atleos (38), Dexterity (35)
 📚 **Source Links:**
 • [Placements](https://tkrcet.ac.in/placements/)
 </t>
@@ -649,205 +554,115 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.4692</t>
+          <t>23.2558</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>117a5cdb-f8cb-431b-9d6e-e9e2b4b9e49a</t>
+          <t>368ad839-5575-4124-9803-f04d2f6be8f4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-27 15:05:01</t>
+          <t>2026-03-03 01:17:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>where the college is located?</t>
+          <t>List all CSE students.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">📌 **Quick Links:**
-• [TKRCET Website](https://tkrcet.ac.in/)
-Hey there, future TKRCETian! I'm stoked to be your friendly College Buddy. Don't worry if you have any questions or need help with anything - I've got your back!
-So, you're looking for some info about our amazing college, right? Well, let me tell you, we're proud of what we do here at TKRCET.
-First off, regarding your questions:
-* We don't have a medical facility on campus, but we do have a tie-up with nearby hospitals and medical centers. If you need any serious medical attention, our staff will help you get in touch with the right people.
-* Our college was indeed established in **2002**, and it's been growing ever since!
-* The contact number of the college is indeed **+91 9849477550**. You can give them a call if you need any info or just want to chat.
-Now, about your question: Where is our college located? Well, we're situated in Hyderabad, Telangana, India! Specifically, our address is:
-**TKRCET College**
-**Near Kukatpally Cross Road**
-**Hyderabad, Telangana - 500072**
-We're easily accessible by public transport or even a short drive from the city center. If you need help finding us, just ask anyone around, and they'll point you in the right direction!
-By the way, did you know that we have a pretty cool campus life here at TKRCET? We've got awesome facilities, including sports fields, libraries, and more! Our students are always busy with extracurricular activities, clubs, and whatnot.
-If you have any more questions or just want to chat about TKRCET, feel free to ask me anytime! I'm all ears (and ready to help).
-📚 **Source Links:**
-• [TKRCET Website](https://tkrcet.ac.in/)
-</t>
+          <t>Summary (526 students found):
+• Placed students: 131 out of 526
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.04
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 526
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [TKRCET Home](https://tkrcet.ac.in/)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>67.6896</t>
+          <t>0.0384</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7fb761db-301a-462b-84de-b3f198e51718</t>
+          <t>41ad18bf-764c-4a0b-9631-84af449bc5fe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.8</v>
+          <t>SQL Database</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-27 15:05:11</t>
+          <t>2026-03-03 01:17:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What courses are offered in the College?</t>
+          <t>where the college is located?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">**Courses Offered:**
-🎓 **B.Tech:** CSE, CSE-AIML, CSE-DS, ECE, EEE, IT, Mechanical, Civil
-🎓 **M.Tech/MBA:** M.Tech in CSE, M.Tech in Power Electronics, MBA
-📌 **Quick Links:**
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm your TKRCET College Buddy!
+Unfortunately, the provided context doesn't mention the location of the college. It only provides information about the college's history, affiliations, and other details. If you need to know the location, I'd be happy to help you search for it!
+📚 **Source Links:**
 • [TKRCET Website](https://tkrcet.ac.in/)
 </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0006</t>
+          <t>14.1009</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ec4cf31c-cf18-40fc-81af-f51593a8ffa3</t>
+          <t>c8342ff6-d6b2-4d14-9471-35875df6d244</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.8</v>
+          <t>RAG</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-27 15:06:54</t>
+          <t>2026-03-03 01:18:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How to check the results?</t>
+          <t>How many students got placed in 2024?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">📌 **Quick Links:**
 • [TKRCET Website](https://tkrcet.ac.in/)
-Hey there! I'm super excited to help you with all your TKRCET-related queries. Don't worry about any typos or unclear questions - we'll get everything sorted out!
-So, you want to know how to check the results? Easy peasy! Here's what you need to do:
-**Step 1: Visit the College Website**
-Head over to our college website ([insert website URL]) and navigate to the "Results" section. You can usually find it under the "Student Corner" or "Academic" tab.
-**Step 2: Click on the Relevant Exam**
-Look for the exam you want to check results for (e.g., B.Tech I Year I Sem, MBA II Yr I &amp; II Sem, etc.). Click on that link to proceed.
-**Step 3: Enter Your Roll Number and Other Details**
-You'll need to enter your roll number, student ID, or other required details to access the result page. Make sure you have these details handy!
-**Step 4: Download/Print Your Results**
-Once you've entered all the necessary details, click on the "Download" or "Print" button to get your results. You can usually download a PDF copy of your results.
-That's it! If you're still having trouble finding the results section or need help with anything else, feel free to ask, and I'll guide you through it.
-By the way, have you checked out our college's social media pages? We often post updates about exam schedules, result announcements, and other important notifications. You can find us on Facebook ([insert Facebook URL]) and Twitter ([insert Twitter URL]).
+I'm the TKRCET College Buddy!
+Unfortunately, I don't have information on the number of students who got placed in 2024. The provided context only mentions the placement rate for previous years (21%). If you're looking for the latest data, I recommend checking with the college administration or the official website for more recent updates.
 📚 **Source Links:**
 • [TKRCET Website](https://tkrcet.ac.in/)
 </t>
@@ -855,66 +670,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>100.8505</t>
+          <t>15.2502</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>174601ae-6b3d-47fb-afcd-9c30d36cc89f</t>
+          <t>b74bf903-1c4e-438b-823f-5f49bdb50d5a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27 15:07:57</t>
+          <t>2026-03-03 01:18:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>what is the minimum attendance required?</t>
+          <t>What courses are offered in the College?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">📌 **Quick Links:**
 • [TKRCET Website](https://tkrcet.ac.in/)
-I'm stoked to help you out with all your TKRCET-related queries! So, let's get started!
-You're right that we don't have the exact info on the title and source for attendance calculation. But I can definitely guide you on how it works.
-According to JNTUH norms, **75% attendance** is mandatory per subject. This means if you miss a class or two, but attend most of your classes, you'll still be considered as having attended 75%. However, if you miss more than 25% of the total classes in a semester, you might not be able to pass that particular subject.
-Now, about the minimum attendance requirement... Since it's mandatory to have **75% attendance** per subject, I'd say the minimum overall attendance requirement is also around 75%. However, please note that this can vary depending on the specific rules and regulations of each department or faculty within the college.
-To get more accurate info, I recommend checking with your department's office or the student affairs office. They should be able to provide you with the most up-to-date information on attendance requirements.
-Also, just a heads-up: if you're having trouble meeting the attendance requirement, there are some options available to help you catch up. For example, some departments offer special classes or make-ups for students who miss classes due to illness or other reasons.
-Let me know if you have any more questions or concerns! I'm here to help
+The college offers the following courses:
+1. B.Tech:
+   - CSE
+   - CSE-AIML
+   - CSE-DS
+   - ECE
+   - EEE
+   - IT
+   - Mechanical
+   - Civil
+2. M.Tech/MBA:
+   - M.Tech in CSE
+   - M.Tech in Power Electronics
+   - MBA
 📚 **Source Links:**
 • [TKRCET Website](https://tkrcet.ac.in/)
 </t>
@@ -922,112 +720,2686 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>59.8691</t>
+          <t>35.2374</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0a492e42-0464-43f6-ad85-1867265c3390</t>
+          <t>886eefa2-4ec9-4394-ada4-8696a3a7bcac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.8</v>
+          <t>Knowledge Base</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27 15:08:59</t>
+          <t>2026-03-03 01:19:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>How to check the results?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>30.0521</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>d700326e-2f1b-48fc-9901-aa424c54b2fc</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:20:11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>what is the minimum attendance required?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+The minimum attendance required is 75%.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27.2112</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>616d851c-202d-475a-81c8-d281dc161411</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:20:34</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Do college have any dress code or uniform</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Yes, there is a dress code policy in the college. Students are expected to follow the guidelines and generally wear formal attire.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12.4638</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3971f311-b6a1-48f5-ae6e-d8c61b0a3105</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:21:06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>who got placed in savantis in 2024</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm the TKRCET College Buddy!
+Unfortunately, I don't have information on students who were placed at Savantis in 2024. The provided context only mentions that Savantis is one of the top recruiters with 56 placements, but it doesn't provide a list of specific students or their placement details for the year 2024.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>21.1499</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>070fc962-538d-4b5c-97f6-9e137504cf63</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:21:47</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>What is the fee structure for MBA program?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Fee Structure](https://tkrcet.ac.in/fee-structure/)
+• [MBA Department](https://tkrcet.ac.in/mba/)
+The tuition fee for the MBA program is approximately ₹50,000 per year.
+📚 **Source Links:**
+• [Fee Structure](https://tkrcet.ac.in/fee-structure/)
+• [MBA Department](https://tkrcet.ac.in/mba/)
+</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>26.9665</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>865f70d6-7fb3-4028-a5ab-46d71f1c1806</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:22:20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Give me the list of students placed in 2023</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I don't have information on the number of students placed in 2023. The provided context only mentions the placement statistics for previous years (2019).
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>18.8366</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>b537299a-7e83-4677-b232-ba5809b2ba63</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:22:37</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>who is topper of CSE department in 2024</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Summary (526 students found):
+• Placed students: 131 out of 526
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.04
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 526
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [TKRCET Home](https://tkrcet.ac.in/)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0726</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7d9e3b99-a0cb-4e8f-94bf-828a7ce930ae</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:22:51</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>how many cse students got placed in jbm group?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Summary (131 students found):
+• Placed students: 131 out of 131
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.88
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 131
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [Placement Cell](https://tkrcet.ac.in/placement/)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0428</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6636a529-9879-41cd-867d-77b185b48429</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:23:18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>what is the female pass percentage in 2025?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I don't have information on the female pass percentage for 2025. The provided context only mentions the total number of students (1648) but does not provide specific details on gender-wise pass percentages.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>14.7040</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>62d96915-e8b0-492a-820e-eb1ca21497cb</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:23:55</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>who is head of library?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Library](https://tkrcet.ac.in/library/)
+The Head of Library (HOD) is not specified in the provided context, but it can be inferred that the Department Library HOD and faculty Incharge controls the functionality of the department library.
+📚 **Source Links:**
+• [Library](https://tkrcet.ac.in/library/)
+</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>21.5903</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>28b91668-8123-4d0b-b5de-5a4522e8b3e2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:24:14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>which companies visited for placements in 2024?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top Recruiting Companies:
+• Savantis: 56 students
+• Ncr Atleos: 38 students
+• Dexterity: 35 students
+• Qspiders: 16 students
+• Jbm Group: 14 students
+• Camelq Software Solutions: 13 students
+• Is Squared: 10 students
+• Excelr Edtech Pvt: 8 students
+• Cognizant: 8 students
+• Smartbrains: 6 students
+</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.0244</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>04498c27-0b8f-4c5f-9ba7-1aa32600f52f</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:24:37</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>do college have hostel facilities?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+Yes, the college has separate hostels for boys and girls.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9.9624</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>025cb822-8ea5-4b98-80e5-5792fe77e774</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:26:26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tell me about the college infrastructure.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+**College Infrastructure**
+As per the provided context, the TKRCET College has a modern and well-equipped infrastructure that supports advanced learning. Here are some key features of the college infrastructure:
+1. **State-of-the-Art Laboratories**: The college is equipped with modern laboratories that provide students with hands-on experience in their respective fields.
+2. **Smart Classrooms**: The college has smart classrooms that utilize technology to enhance the learning experience for students.
+3. **Wi-Fi-Enabled Learning Spaces**: The college provides Wi-Fi-enabled learning spaces that enable students to access digital resources and stay connected with the world.
+4. **Digital Libraries**: The college has digital libraries that provide students with access to a vast collection of e-books, journals, and other digital resources.
+5. **Training &amp; Placement Cell**: The college has a dedicated Training &amp; Placement Cell that focuses on achieving 100% placement for its students.
+Overall, the college infrastructure is designed to support advanced learning and provide students with the skills and knowledge needed to succeed in their chosen fields.
+**Additional Information**
+* The college campus is equipped with modern facilities such as smart classrooms, Wi-Fi-enabled learning spaces, and digital libraries.
+* The college has a strong focus on innovation and research, with a goal of ensuring quality education and institutional credibility.
+* The college is affiliated with JNTUH (Jawaharlal Nehru Technological University Hyderabad) and follows UGC 2(f) &amp; 12(B) guidelines to ensure accreditation.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>93.9351</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>05808d42-6d11-4273-83c7-67e22148dbcf</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:27:27</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Do college have transport facilities?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [About Campus](https://tkrcet.ac.in/about-the-campus/)
+Yes, the college provides transportation for students and staff through its fleet of buses connecting various parts of Hyderabad city to the campus.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [About Campus](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>43.8046</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7eed41d2-19e6-421f-a3d3-6dd9245f2636</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:29:15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>what is the procedure to apply for scholarships?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Hello! I'm your TKRCET College Buddy. I'd be happy to help you with the scholarship application procedure at our college.
+**Step-by-Step Procedure to Apply for Scholarships:**
+1. **Eligibility Check**: Ensure that you meet the eligibility criteria for government scholarships (SC/ST/BC/EBC/Minority) and merit-based scholarships offered by our college.
+2. **Gather Required Documents**: Collect the necessary documents, including:
+	* **Caste Certificate** (if applicable)
+	* **Income Certificate**
+	* **Identity Proof** (e.g., Aadhaar Card, PAN Card)
+	* **Qualification Certificates** (10th and 12th standards)
+3. **Fill Online Application Form**: Visit the online state government portal to fill out the application form for government scholarships.
+4. **Submit Application Form**: Submit the application form along with the required documents to the designated authority.
+5. **Merit-based Scholarship Application**: If you're applying for our college's merit-based scholarship, follow these steps:
+	* Check your eligibility criteria on our college website or contact our Vice Principal (HoD of CSE &amp; Dean Academics), Dr. A. Suresh Rao.
+	* Fill out the online application form provided by our college.
+	* Submit the application form along with the required documents to our college administration.
+6. **Financial Aid Processing**: If you're applying for financial aid, visit the online state government portal to
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>91.8647</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>a3897c65-1b14-48fb-b200-bb207422e89b</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:30:04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>do college provide training before drive?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Yes, the college provides training before drives in aptitude, communication, and technical skills.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>32.5640</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>07c45802-6f0b-47f5-bddc-e1f3af50dced</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:30:48</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>who is head of placement cell?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>30.0628</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>451c1eec-4c53-459b-95d3-4e6300749f1c</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:32:12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>what is the highest package offered in 2024?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I don't have information on the highest package offered in 2024. The provided context only mentions the top recruiters for the college, which are Savantis (56), Ncr Atleos (38), and Dexterity (35). It does not provide details on the highest package offered to students in 2024.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>68.2939</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>245d407a-8f90-45e9-88aa-94f46ebb60de</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:33:05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>who got highest package in 2025?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>30.0456</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>5dd80c0e-7194-4b21-acc0-23c2ba606a5d</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:34:03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>what is full name of college?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm the TKRCET College Buddy!
+According to the provided context, I don't have enough information to provide the full name of the college. However, I can tell you that it's affiliated with JNTUH (Jawaharlal Nehru Technological University Hyderabad). If you need more information, feel free to ask!
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>42.8894</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0a5ff7c3-4a4e-4741-8077-0026973efa4c</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:34:33</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Do college have any sports facilities?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+Yes, the college has 5-acre playground with cricket, basketball, indoor &amp; outdoor games facilities.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>17.1597</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>e668fbfb-fff2-42ac-a7c8-c1aef12de79e</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:36:03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>How to take admission in college hostel?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Admissions](https://tkrcet.ac.in/admission-procedure/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+**Welcome to TKRCET College Buddy!**
+I'm here to help you with your queries about TKRCET College. Based on the provided context, I'll guide you through the process of taking admission in the college hostel.
+**Yes, the college provides hostel facilities**, and it's a great option for students who want to live on campus. Here's how you can take admission in the college hostel:
+1. **Meet the Eligibility Criteria**: Check if you meet the eligibility criteria set by the college. This may include factors like academic performance, age, and other requirements.
+2. **Apply for Admission**: Submit an application for admission to the college, which typically includes providing personal details, academic documents, and other required information.
+3. **Fill Hostel Application Form**: Once your admission is approved, fill out the hostel application form, which may be available on the college website or at the admissions office.
+4. **Pay Hostel Fees**: Pay the hostel fees, which may vary depending on the type of accommodation and duration of stay.
+5. **Attend Hostel Orientation**: Attend a mandatory orientation session for new hostel residents, where you'll meet other students, faculty members, and learn about college rules and regulations.
+6. **Get Assigned Room**: After completing the above steps, you'll be assigned a room in the hostel, and you can move in.
+**Additional Tips:**
+* Make sure to apply early, as hostel seats are limited.
+* Be prepared for a strict
+📚 **Source Links:**
+• [Admissions](https://tkrcet.ac.in/admission-procedure/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>75.5308</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>dc602ba8-3e34-403a-acd5-7a491cc837d0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:36:57</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>give me contact details of college hostel</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+I don't have the exact contact details of the college hostel. However, I can suggest some possible ways to get in touch with them:
+1. Contact the Vice Principal (Dr. A. Suresh Rao) or the Principal (Dr. D. V. Ravi Shankar) through their official email addresses or phone numbers.
+2. Check the college's website for a hostel contact page or a list of contact details.
+3. Reach out to the college's administration office directly.
+Please note that I don't have the specific contact information available in the provided context.
+📚 **Source Links:**
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>39.9802</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>5594547e-d6b4-4d48-8005-a13ce817bb61</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Bot Answer</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval Confidence (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Latency (s)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Server Time (s)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Faithfulness % (LLM)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance % (LLM)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Completeness % (LLM)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>BERTScore F1 %</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Link Validity</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:15:54</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>What is the attendance criteria?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+The attendance criteria for TKRCET is 75% attendance per subject, as per JNTUH norms.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.206</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.7916</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0/2 Valid</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>90.06999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:16:31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What is the NAAC grade of the college?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [NAAC](https://tkrcet.ac.in/naac-2/)
+The NAAC grade of the college is not mentioned in the provided context.
+📚 **Source Links:**
+• [NAAC](https://tkrcet.ac.in/naac-2/)
+</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19.9354</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>33</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0/2 Valid</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:17:09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tell me placement statistics.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Placements](https://tkrcet.ac.in/placements/)
+Hello! I'm your TKRCET College Buddy. 
+Here's the placement statistics:
+- Total Students: 1648
+- Placed Students: 351 (Rate: 21%)
+- Top Recruiters: Savantis (56), Ncr Atleos (38), Dexterity (35)
+📚 **Source Links:**
+• [Placements](https://tkrcet.ac.in/placements/)
+</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23.2558</v>
+      </c>
+      <c r="H4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>87.84999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:17:19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>List all CSE students.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Summary (526 students found):
+• Placed students: 131 out of 526
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.04
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 526
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [TKRCET Home](https://tkrcet.ac.in/)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1/1 Valid</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:17:44</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>where the college is located?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm your TKRCET College Buddy!
+Unfortunately, the provided context doesn't mention the location of the college. It only provides information about the college's history, affiliations, and other details. If you need to know the location, I'd be happy to help you search for it!
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>66</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14.1009</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>88.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:18:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>How many students got placed in 2024?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm the TKRCET College Buddy!
+Unfortunately, I don't have information on the number of students who got placed in 2024. The provided context only mentions the placement rate for previous years (21%). If you're looking for the latest data, I recommend checking with the college administration or the official website for more recent updates.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>44</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15.2502</v>
+      </c>
+      <c r="H7" t="n">
+        <v>100</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>88.98999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:19:03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>What courses are offered in the College?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+The college offers the following courses:
+1. B.Tech:
+   - CSE
+   - CSE-AIML
+   - CSE-DS
+   - ECE
+   - EEE
+   - IT
+   - Mechanical
+   - Civil
+2. M.Tech/MBA:
+   - M.Tech in CSE
+   - M.Tech in Power Electronics
+   - MBA
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>63</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G8" t="n">
+        <v>35.2374</v>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>91.70999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:19:43</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>How to check the results?</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">📌 **Quick Links:**
-• [TKRCET Website](https://tkrcet.ac.in/)
-You're looking for info about the dress code at TKRCET! Don't worry, I've got you covered!
-According to our college guidelines, yes, there is a dress code policy in place. Students are expected to follow the dress code guidelines, which generally recommend formal attire.
-Here's a quick rundown of what you can expect:
-• **Dress Code:** Formal and neat attire is recommended.
-• **Uniform:** No specific uniform is required, but students are encouraged to wear college-approved casual wear.
-• **No Jeans or Torn Clothes:** Sorry, jeans and torn clothes aren't allowed on campus!
-• **Respectful Attire:** Avoid revealing or provocative clothing that may be considered disrespectful.
-If you're unsure about what's acceptable, you can always check with the college administration or your department head (like Dr. A. Suresh Rao, our HoD of CSE and Dean Academics) for guidance.
-By the way, have you checked out our college's website or social media channels? They usually post updates on important policies and guidelines!
-Let me know if you have any other questions!
-📚 **Source Links:**
-• [TKRCET Website](https://tkrcet.ac.in/)
-</t>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>59.6646</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>cdc4b3ad-8b7f-424e-8112-021be9f15287</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30.0521</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0.8</v>
+      <c r="M9" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:20:20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>what is the minimum attendance required?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+The minimum attendance required is 75%.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>71</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27.2112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>91.23999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:20:44</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Do college have any dress code or uniform</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Yes, there is a dress code policy in the college. Students are expected to follow the guidelines and generally wear formal attire.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>65</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.4638</v>
+      </c>
+      <c r="H11" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>90.84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:21:19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>who got placed in savantis in 2024</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm the TKRCET College Buddy!
+Unfortunately, I don't have information on students who were placed at Savantis in 2024. The provided context only mentions that Savantis is one of the top recruiters with 56 placements, but it doesn't provide a list of specific students or their placement details for the year 2024.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21.1499</v>
+      </c>
+      <c r="H12" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>87.41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:22:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>What is the fee structure for MBA program?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Fee Structure](https://tkrcet.ac.in/fee-structure/)
+• [MBA Department](https://tkrcet.ac.in/mba/)
+The tuition fee for the MBA program is approximately ₹50,000 per year.
+📚 **Source Links:**
+• [Fee Structure](https://tkrcet.ac.in/fee-structure/)
+• [MBA Department](https://tkrcet.ac.in/mba/)
+</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>26.9665</v>
+      </c>
+      <c r="H13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4/4 Valid</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>91.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:22:37</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Give me the list of students placed in 2023</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I don't have information on the number of students placed in 2023. The provided context only mentions the placement statistics for previous years (2019).
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.8366</v>
+      </c>
+      <c r="H14" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>88.08</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:22:50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>who is topper of CSE department in 2024</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Summary (526 students found):
+• Placed students: 131 out of 526
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.04
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 526
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [TKRCET Home](https://tkrcet.ac.in/)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1/1 Valid</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:23:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>how many cse students got placed in jbm group?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Summary (131 students found):
+• Placed students: 131 out of 131
+• Top recruiters: Savantis, Dexterity, Ncr Atleos
+• Average CGPA: 7.88
+• Highest CGPA: 9.31
+• Branch-wise: CSE: 131
+(Individual student data is protected. Please contact administration for specific records.)
+Related Links:
+- [Placement Cell](https://tkrcet.ac.in/placement/)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="H16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0/1 Valid</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:23:33</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>what is the female pass percentage in 2025?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I don't have information on the female pass percentage for 2025. The provided context only mentions the total number of students (1648) but does not provide specific details on gender-wise pass percentages.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.704</v>
+      </c>
+      <c r="H17" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>88.87</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:24:13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>who is head of library?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Library](https://tkrcet.ac.in/library/)
+The Head of Library (HOD) is not specified in the provided context, but it can be inferred that the Department Library HOD and faculty Incharge controls the functionality of the department library.
+📚 **Source Links:**
+• [Library](https://tkrcet.ac.in/library/)
+</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21.5903</v>
+      </c>
+      <c r="H18" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>92.15000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:24:26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>which companies visited for placements in 2024?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top Recruiting Companies:
+• Savantis: 56 students
+• Ncr Atleos: 38 students
+• Dexterity: 35 students
+• Qspiders: 16 students
+• Jbm Group: 14 students
+• Camelq Software Solutions: 13 students
+• Is Squared: 10 students
+• Excelr Edtech Pvt: 8 students
+• Cognizant: 8 students
+• Smartbrains: 6 students
+</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:24:51</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>do college have hostel facilities?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+Yes, the college has separate hostels for boys and girls.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>76</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9.962400000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2/4 Valid</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>90.93000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:26:42</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tell me about the college infrastructure.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+**College Infrastructure**
+As per the provided context, the TKRCET College has a modern and well-equipped infrastructure that supports advanced learning. Here are some key features of the college infrastructure:
+1. **State-of-the-Art Laboratories**: The college is equipped with modern laboratories that provide students with hands-on experience in their respective fields.
+2. **Smart Classrooms**: The college has smart classrooms that utilize technology to enhance the learning experience for students.
+3. **Wi-Fi-Enabled Learning Spaces**: The college provides Wi-Fi-enabled learning spaces that enable students to access digital resources and stay connected with the world.
+4. **Digital Libraries**: The college has digital libraries that provide students with access to a vast collection of e-books, journals, and other digital resources.
+5. **Training &amp; Placement Cell**: The college has a dedicated Training &amp; Placement Cell that focuses on achieving 100% placement for its students.
+Overall, the college infrastructure is designed to support advanced learning and provide students with the skills and knowledge needed to succeed in their chosen fields.
+**Additional Information**
+* The college campus is equipped with modern facilities such as smart classrooms, Wi-Fi-enabled learning spaces, and digital libraries.
+* The college has a strong focus on innovation and research, with a goal of ensuring quality education and institutional credibility.
+* The college is affiliated with JNTUH (Jawaharlal Nehru Technological University Hyderabad) and follows UGC 2(f) &amp; 12(B) guidelines to ensure accreditation.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>57</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G21" t="n">
+        <v>93.93510000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>100</v>
+      </c>
+      <c r="K21" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>91.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:27:42</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Do college have transport facilities?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [About Campus](https://tkrcet.ac.in/about-the-campus/)
+Yes, the college provides transportation for students and staff through its fleet of buses connecting various parts of Hyderabad city to the campus.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+• [About Campus](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>59</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G22" t="n">
+        <v>43.8046</v>
+      </c>
+      <c r="H22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2/4 Valid</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>90.48999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:29:31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>what is the procedure to apply for scholarships?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Hello! I'm your TKRCET College Buddy. I'd be happy to help you with the scholarship application procedure at our college.
+**Step-by-Step Procedure to Apply for Scholarships:**
+1. **Eligibility Check**: Ensure that you meet the eligibility criteria for government scholarships (SC/ST/BC/EBC/Minority) and merit-based scholarships offered by our college.
+2. **Gather Required Documents**: Collect the necessary documents, including:
+	* **Caste Certificate** (if applicable)
+	* **Income Certificate**
+	* **Identity Proof** (e.g., Aadhaar Card, PAN Card)
+	* **Qualification Certificates** (10th and 12th standards)
+3. **Fill Online Application Form**: Visit the online state government portal to fill out the application form for government scholarships.
+4. **Submit Application Form**: Submit the application form along with the required documents to the designated authority.
+5. **Merit-based Scholarship Application**: If you're applying for our college's merit-based scholarship, follow these steps:
+	* Check your eligibility criteria on our college website or contact our Vice Principal (HoD of CSE &amp; Dean Academics), Dr. A. Suresh Rao.
+	* Fill out the online application form provided by our college.
+	* Submit the application form along with the required documents to our college administration.
+6. **Financial Aid Processing**: If you're applying for financial aid, visit the online state government portal to
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>64</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G23" t="n">
+        <v>91.8647</v>
+      </c>
+      <c r="H23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:30:18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>do college provide training before drive?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+Yes, the college provides training before drives in aptitude, communication, and technical skills.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>61</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="G24" t="n">
+        <v>32.564</v>
+      </c>
+      <c r="H24" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>88.14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:31:03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>who is head of placement cell?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>30.115</v>
+      </c>
+      <c r="G25" t="n">
+        <v>30.0628</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:32:34</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>what is the highest package offered in 2024?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I don't have information on the highest package offered in 2024. The provided context only mentions the top recruiters for the college, which are Savantis (56), Ncr Atleos (38), and Dexterity (35). It does not provide details on the highest package offered to students in 2024.
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>40</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>68.29389999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K26" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>90.01000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:33:19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>who got highest package in 2025?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>I couldn't understand the student query. Please specify student ID, name, department, or conditions.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30.101</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30.0456</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:34:15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>what is full name of college?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+I'm the TKRCET College Buddy!
+According to the provided context, I don't have enough information to provide the full name of the college. However, I can tell you that it's affiliated with JNTUH (Jawaharlal Nehru Technological University Hyderabad). If you need more information, feel free to ask!
+📚 **Source Links:**
+• [TKRCET Website](https://tkrcet.ac.in/)
+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>65</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="G28" t="n">
+        <v>42.8894</v>
+      </c>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2/2 Valid</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>90.52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:34:47</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Do college have any sports facilities?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+Yes, the college has 5-acre playground with cricket, basketball, indoor &amp; outdoor games facilities.
+📚 **Source Links:**
+• [IT Department](https://tkrcet.ac.in/information-technology/)
+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>66</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="G29" t="n">
+        <v>17.1597</v>
+      </c>
+      <c r="H29" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0/2 Valid</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>89.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-03 01:36:17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>How to take admission in college hostel?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📌 **Quick Links:**
+• [Admissions](https://tkrcet.ac.in/admission-procedure/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+**Welcome to TKRCET College Buddy!**
+I'm here to help you with your queries about TKRCET College. Based on the provided context, I'll guide you through the process of taking admission in the college hostel.
+**Yes, the college provides hostel facilities**, and it's a great option for students who want to live on campus. Here's how you can take admission in the college hostel:
+1. **Meet the Eligibility Criteria**: Check if you meet the eligibility criteria set by the college. This may include factors like academic performance, age, and other requirements.
+2. **Apply for Admission**: Submit an application for admission to the college, which typically includes providing personal details, academic documents, and other required information.
+3. **Fill Hostel Application Form**: Once your admission is approved, fill out the hostel application form, which may be available on the college website or at the admissions office.
+4. **Pay Hostel Fees**: Pay the hostel fees, which may vary depending on the type of accommodation and duration of stay.
+5. **Attend Hostel Orientation**: Attend a mandatory orientation session for new hostel residents, where you'll meet other students, faculty members, and learn about college rules and regulations.
+6. **Get Assigned Room**: After completing the above steps, you'll be assigned a room in the hostel, and you can move in.
+**Additional Tips:**
+* Make sure to apply early, as hostel seats are limited.
+* Be prepared for a strict
+📚 **Source Links:**
+• [Admissions](https://tkrcet.ac.in/admission-procedure/)
+• [Campus Life](https://tkrcet.ac.in/about-the-campus/)
+</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75.5308</v>
+      </c>
+      <c r="H30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>4/4 Valid</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>93.73999999999999</v>
       </c>
     </row>
   </sheetData>
